--- a/maintenance/CleanAirSystem_Maintenance_Tracker_Template.xlsx
+++ b/maintenance/CleanAirSystem_Maintenance_Tracker_Template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U7"/>
+  <dimension ref="A1:Y7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,6 +534,26 @@
           <t>Last_Done_Draw</t>
         </is>
       </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Required Parts</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Planning months</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Estimated duration min</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -613,6 +633,22 @@
         <v>0</v>
       </c>
       <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Pre-filter element; Pre-filter seal/gasket; IPA wipes / cleaning cloth</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Per-Draw/Startup</t>
+        </is>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -692,6 +728,22 @@
         <v>0</v>
       </c>
       <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Pre-filter element; Pre-filter seal/gasket; IPA wipes / cleaning cloth</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Routine</t>
+        </is>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -777,6 +829,22 @@
         <v>0</v>
       </c>
       <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Pre-filter element; Pre-filter seal/gasket; IPA wipes / cleaning cloth</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -862,6 +930,22 @@
         <v>0</v>
       </c>
       <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Pre-filter element; Pre-filter seal/gasket; HEPA filter element; HEPA gasket/seal; IPA wipes / cleaning cloth</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>6-Month</t>
+        </is>
+      </c>
+      <c r="X5" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -941,6 +1025,22 @@
         <v>0</v>
       </c>
       <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Pre-filter element; Pre-filter seal/gasket; HEPA filter element; HEPA gasket/seal; IPA wipes / cleaning cloth</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>On-Condition</t>
+        </is>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>45</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1020,6 +1120,22 @@
         <v>0</v>
       </c>
       <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Pre-filter element; Pre-filter seal/gasket; HEPA filter element; HEPA gasket/seal; IPA wipes / cleaning cloth</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>On-Condition</t>
+        </is>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>45</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/maintenance/CleanAirSystem_Maintenance_Tracker_Template.xlsx
+++ b/maintenance/CleanAirSystem_Maintenance_Tracker_Template.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y7"/>
+  <dimension ref="A1:AB7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,6 +554,21 @@
           <t>Estimated duration min</t>
         </is>
       </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_UV1</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_UV2</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Last_Done_Hours_Furnace</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -594,9 +609,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>Clean Air System (SG Controls)</t>
@@ -620,19 +632,20 @@
           <t>Airflow too high can displace fibre line; airflow too low may not protect from particulates.</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U2" t="n">
+        <v>93</v>
+      </c>
       <c r="V2" t="inlineStr">
         <is>
           <t>Pre-filter element; Pre-filter seal/gasket; IPA wipes / cleaning cloth</t>
@@ -648,6 +661,15 @@
       </c>
       <c r="Y2" t="n">
         <v>20</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>249</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="3">
@@ -689,9 +711,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>Clean Air System (SG Controls)</t>
@@ -715,19 +734,20 @@
           <t>Incorrect clean-air setting can cause fibre displacement and potential contacts (top disc / cooling tubes).</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U3" t="n">
+        <v>93</v>
+      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>Pre-filter element; Pre-filter seal/gasket; IPA wipes / cleaning cloth</t>
@@ -743,6 +763,15 @@
       </c>
       <c r="Y3" t="n">
         <v>20</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>249</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="4">
@@ -784,7 +813,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>months</t>
@@ -816,19 +844,14 @@
           <t>Service frequency may vary based on usage, intake cleanliness, volume of air, and working environment.</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
+          <t>2026-03-08</t>
+        </is>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
-      <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr">
         <is>
           <t>Pre-filter element; Pre-filter seal/gasket; IPA wipes / cleaning cloth</t>
@@ -885,7 +908,6 @@
           <t>calendar</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>months</t>
@@ -917,19 +939,14 @@
           <t>Isolate electrical power before removing/installing/servicing filters.</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
-        </is>
-      </c>
-      <c r="S5" t="n">
-        <v>0</v>
+          <t>2025-10-09</t>
+        </is>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
-      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr">
         <is>
           <t>Pre-filter element; Pre-filter seal/gasket; HEPA filter element; HEPA gasket/seal; IPA wipes / cleaning cloth</t>
@@ -986,9 +1003,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>Clean Air System (SG Controls)</t>
@@ -1012,19 +1026,20 @@
           <t>Ensure electrical power is isolated before servicing.</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U6" t="n">
+        <v>93</v>
+      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>Pre-filter element; Pre-filter seal/gasket; HEPA filter element; HEPA gasket/seal; IPA wipes / cleaning cloth</t>
@@ -1040,6 +1055,15 @@
       </c>
       <c r="Y6" t="n">
         <v>45</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>249</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1009</v>
       </c>
     </row>
     <row r="7">
@@ -1081,9 +1105,6 @@
           <t>event</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>Clean Air System (SG Controls)</t>
@@ -1107,19 +1128,20 @@
           <t>Working at height: use guard rails/harness; prevent items falling. Isolate electrical power before servicing.</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
-          <t>2026-01-28</t>
+          <t>2026-04-04</t>
         </is>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1009</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
+        <v>1009</v>
+      </c>
+      <c r="U7" t="n">
+        <v>93</v>
+      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>Pre-filter element; Pre-filter seal/gasket; HEPA filter element; HEPA gasket/seal; IPA wipes / cleaning cloth</t>
@@ -1135,6 +1157,15 @@
       </c>
       <c r="Y7" t="n">
         <v>45</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>249</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>249</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1009</v>
       </c>
     </row>
   </sheetData>
